--- a/context_DB/CAR_context_db.xlsx
+++ b/context_DB/CAR_context_db.xlsx
@@ -556,62 +556,62 @@
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>event_count</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ADM3_PCODE</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>event_count</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>ADM3_PCODE</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -696,52 +696,52 @@
           <t>Lobaye</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Military Forces of the Central African Republic (2016-)</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Students (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Around 27 February 2024 (as reported), FACA soldiers in training attacked students in Berongo, coded to Bobangui (Pissa, Mbaiki, Lobaye). Casualties unknown. No information on the injuries. The sources claim that the students had taunted the soldiers.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>Mbaiki</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>Military Forces of the Central African Republic (2016-)</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Students (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Around 27 February 2024 (as reported), FACA soldiers in training attacked students in Berongo, coded to Bobangui (Pissa, Mbaiki, Lobaye). Casualties unknown. No information on the injuries. The sources claim that the students had taunted the soldiers.</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>27 February 2024</t>
         </is>
       </c>
       <c r="AL2" t="n">
@@ -2755,19 +2755,51 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Ouham</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
       <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Change to group/activity</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Central African Republic)</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Movement of forces: On 8 July 2025, an unidentified armed group occupied a primary school in Kouki (Nana-Bakassa, Ouham). Local sources say the armed group outnumbers security forces in the area.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Nana-Bakassa</t>
+        </is>
+      </c>
       <c r="AL25" t="n">
         <v>0.07166409282524312</v>
       </c>
@@ -5400,52 +5432,56 @@
           <t>Vakaga</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="Z55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack ---- Other</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Central African Republic) ---- Unidentified Armed Group (Sudan) ---- Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic) ---- Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Civilians (Chad); Labor Group (Central African Republic); Labor Group (Chad); Muslim Group (Central African Republic); Muslim Group (Chad); Students (Central African Republic); Students (Chad) ---- Students (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>On 22 March 2025, an unidentified armed group ambushed and attacked traveling traders, and children from the Central African Republic and Chad, 12 kilometers from Boromata, closest to Keche (Ouandja, Birao, Central African Republic). 2 children were killed and three others went missing. The children were traveling to attend Koranic schools. ---- On 11 July 2025, an unidentified armed group from Sudan attacked and killed 2 civilians, including a student in Am-Dafock (Ridina, Birao, Vakaga). ---- Displacement: Around 16 July 2025 (as reported), hundreds of civilians from Zaire, Kafao and Bachama (coded separately) arrived in Birao (Ridina, Birao, Vakaga), after fleeing violence. Many are sheltering in schools and face shortages of food and medicine.</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>2025-03-22 ---- 2025-07-11 ---- 2025-07-16</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
         <is>
           <t>Birao</t>
-        </is>
-      </c>
-      <c r="AA55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Group (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Civilians (Chad); Labor Group (Central African Republic); Labor Group (Chad); Muslim Group (Central African Republic); Muslim Group (Chad); Students (Central African Republic); Students (Chad)</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>On 22 March 2025, an unidentified armed group ambushed and attacked traveling traders, and children from the Central African Republic and Chad, 12 kilometers from Boromata, closest to Keche (Ouandja, Birao, Central African Republic). 2 children were killed and three others went missing. The children were traveling to attend Koranic schools.</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>22 March 2025</t>
         </is>
       </c>
       <c r="AL55" t="n">
@@ -5968,56 +6004,56 @@
           <t>Basse-Kotto</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="Z61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Mob violence</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Rioters (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Langbachi Communal Group (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>Rioters (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Yakoma Communal Group (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>On 31 October 2024, Langbachi and Yakoma communities clashed in Satema (Kotto-Oubangui, Satema, Basse-Kotto) after a Yakoma student stabbed his Langbachi classmate. Unspecified fatalities, coded as 3. The clashes caused villagers to flee to the Democratic Republic of Congo.</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Satema</t>
-        </is>
-      </c>
-      <c r="AA61" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>Riots</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>Mob violence</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>Rioters (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>Langbachi Communal Group (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Rioters (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Yakoma Communal Group (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>On 31 October 2024, Langbachi and Yakoma communities clashed in Satema (Kotto-Oubangui, Satema, Basse-Kotto) after a Yakoma student stabbed his Langbachi classmate. Unspecified fatalities, coded as 3. The clashes caused villagers to flee to the Democratic Republic of Congo.</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>31 October 2024</t>
         </is>
       </c>
       <c r="AL61" t="n">
@@ -6540,52 +6576,52 @@
           <t>Haut-Mbomou</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>Azande Ani Kpi Gbe (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Labor Group (Central African Republic); Students (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Non-violent activity: Around 28 January 2025 (as reported), Azande Ani Kpi Gbe militia prohibited (means not specified) civilians from continuing their commercial activities and attending school in Obo (Obo, Obo, Haut-Mbomou) after the arrest of some of their colleagues who had been involved in an attack against civilians (coded separately).</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
         <is>
           <t>Obo</t>
-        </is>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>Azande Ani Kpi Gbe (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr"/>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Labor Group (Central African Republic); Students (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>Non-violent activity: Around 28 January 2025 (as reported), Azande Ani Kpi Gbe militia prohibited (means not specified) civilians from continuing their commercial activities and attending school in Obo (Obo, Obo, Haut-Mbomou) after the arrest of some of their colleagues who had been involved in an attack against civilians (coded separately).</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>28 January 2025</t>
         </is>
       </c>
       <c r="AL67" t="n">
@@ -6756,52 +6792,52 @@
           <t>Haut-Mbomou</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>UPC: Union for Peace in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Government of the Central African Republic (2016-)</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Looting: On 18 February 2024, suspected UPC militants looted from delegates of the Ministry of Education between Zemio and Djema, coded to Zemio (Zemio, Zemio, Haut-Mbomou). The delegates were on a mission to assess sites for the construction of a secondary school.</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Zemio</t>
-        </is>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>Looting/property destruction</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>UPC: Union for Peace in the Central African Republic</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Government of the Central African Republic (2016-)</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>Looting: On 18 February 2024, suspected UPC militants looted from delegates of the Ministry of Education between Zemio and Djema, coded to Zemio (Zemio, Zemio, Haut-Mbomou). The delegates were on a mission to assess sites for the construction of a secondary school.</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>18 February 2024</t>
         </is>
       </c>
       <c r="AL69" t="n">
@@ -7050,56 +7086,56 @@
           <t>Bangui</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="Z72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Protests ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Protests</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Attack ---- Peaceful protest ---- Excessive force against protesters ---- Attack ---- Attack ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Military Forces of the Central African Republic (2016-) ---- Protesters (Central African Republic) ---- Protesters (Central African Republic) ---- Military Forces of the Central African Republic (2016-) ---- Unidentified Armed Group (Central African Republic) ---- Protesters (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Students (Central African Republic) ---- Students (Central African Republic) ---- Teachers (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic) ---- Police Forces of the Central African Republic (2016-) ---- Civilians (Central African Republic) ---- Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Students (Central African Republic) ---- Students (Central African Republic); Taxi Drivers (Central African Republic) ---- Private Security Forces (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>On 18 December 2024, a FACA soldier shot and injured a female student near the Avenir School Complex at the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui). The shooting occurred when the FACA forces arrested one civilian and slapped another who retaliated during security checks. The injured student was taken to a community hospital for treatment. ---- On 18 December 2024, students from Avenir School Complex protested near the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui), condemning the shooting of a fellow student by a FACA soldier (coded separately). The protesters demanded accountability and sanctions against the soldier, criticizing the use of firearms during regular security checks. ---- On 11 February 2025, Gbaloko high school students protested in Bangui (Arrondissement 1, Bangui), to condemn an alleged extortion scheme by the school administration, where exams, assignments, and lessons have allegedly become opportunities for financial exploitation. Police fired live ammunition to suppress protesters. ---- On 25 April 2025, FACA soldiers attacked a student working as a commercial motorbike driver (taxi) in Bangui - 3 (Arrondissement 3, Bangui, Bangui). They punched and kicked him until he collapsed, and left him unconscious on the side of a road. They also looted his mobile phone and motorbike. There were no fatalities. The victim spent two days in a coma. ---- On 30 May 2025, an unidentified armed group attacked the AMA scientific high school in the Kokpa neighborhood in Bangui - 4 (Arrondissement 4, Bangui, Bangui), torturing the security guard (was armed only with a baton), who later died. The attackers looted exam papers, equipment, and vandalized offices. ---- On 14 July 2025, a dozen of contractual teachers protested outside the administrative building in Bangui (Arrondissement 1, Bangui, Bangui), to demand three months of unpaid salaries and denounce unequal payments and lack of support for deployment.</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>2024-12-18 ---- 2024-12-18 ---- 2025-02-11 ---- 2025-04-25 ---- 2025-05-30 ---- 2025-07-14</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
         <is>
           <t>Bangui</t>
-        </is>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>Violence against civilians ---- Protests ---- Violence against civilians ---- Protests</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>Attack ---- Excessive force against protesters ---- Attack ---- Peaceful protest</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>Military Forces of the Central African Republic (2016-) ---- Protesters (Central African Republic) ---- Military Forces of the Central African Republic (2016-) ---- Protesters (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>Students (Central African Republic) ---- Students (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic) ---- Police Forces of the Central African Republic (2016-) ---- Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Students (Central African Republic); Taxi Drivers (Central African Republic) ---- Students (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>On 25 April 2025, FACA soldiers attacked a student working as a commercial motorbike driver (taxi) in Bangui - 3 (Arrondissement 3, Bangui, Bangui). They punched and kicked him until he collapsed, and left him unconscious on the side of a road. They also looted his mobile phone and motorbike. There were no fatalities. The victim spent two days in a coma. ---- On 11 February 2025, Gbaloko high school students protested in Bangui (Arrondissement 1, Bangui), to condemn an alleged extortion scheme by the school administration, where exams, assignments, and lessons have allegedly become opportunities for financial exploitation. Police fired live ammunition to suppress protesters. ---- On 18 December 2024, a FACA soldier shot and injured a female student near the Avenir School Complex at the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui). The shooting occurred when the FACA forces arrested one civilian and slapped another who retaliated during security checks. The injured student was taken to a community hospital for treatment. ---- On 18 December 2024, students from Avenir School Complex protested near the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui), condemning the shooting of a fellow student by a FACA soldier (coded separately). The protesters demanded accountability and sanctions against the soldier, criticizing the use of firearms during regular security checks.</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>25 April 2025 ---- 11 February 2025 ---- 18 December 2024 ---- 18 December 2024</t>
         </is>
       </c>
       <c r="AL72" t="n">
@@ -7376,10 +7412,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -7391,13 +7427,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -7406,7 +7444,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -7424,52 +7462,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -7497,6 +7540,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -7610,7 +7664,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
@@ -7618,13 +7673,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D38F0FBE-E9AF-4C25-8EF7-7B25898F0790}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9273CDD-DE4C-45BA-A38B-747F7CE3AA8F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49C9F71F-5F20-4AA6-AE93-5FFDEBBEFC2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A783AD56-D92E-4362-858C-4C02A211AAA8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4D23372-C42D-4A74-BF82-DBF7B27A3429}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E4216EC-8D22-4E22-AC63-85121328CC76}"/>
 </file>
--- a/context_DB/CAR_context_db.xlsx
+++ b/context_DB/CAR_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL75"/>
+  <dimension ref="A1:AL77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">severity (HPC2025) level 5 -- in-school children -- % d'enfants n'ayant pas accès à l'éducation en raison de la circonstance aggravante : L'enfant est associé à des forces armées ou à des groupes armés </t>
+          <t xml:space="preserve">severity (HPC2025) level 5 -- OoS children -- % d'enfants n'ayant pas accès à l'éducation en raison de la circonstance aggravante : L'enfant est associé à des forces armées ou à des groupes armés </t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
@@ -1895,95 +1895,89 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF241</t>
+          <t>CF233</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CF242</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="M16" t="n">
-        <v>111.41</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Sangha-Mbaere</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
       <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Central African Republic)</t>
+        </is>
+      </c>
       <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic)</t>
+        </is>
+      </c>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Around 10 March 2025 (as reported), an unidentified armed group abducted and attacked civilians in Bayanga (Yobe-Sangha, Bayanga, Sangha-Mbaere). The bodies of 2 civilians were found in the river. 1 of the victims was a teacher and the other was a craftsman. The victims were returning from a wake when they were abducted. 2 fatalities.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Bayanga</t>
+        </is>
+      </c>
       <c r="AL16" t="n">
-        <v>0.007781998869506921</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF242</t>
+          <t>CF241</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1992,7 +1986,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CF324</t>
+          <t>CF242</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2001,10 +1995,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="I17" t="n">
-        <v>65.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
@@ -2013,31 +2007,31 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>68.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>122.19</v>
+        <v>111.41</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5.59</v>
+        <v>1.01</v>
       </c>
       <c r="T17" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2065,13 +2059,13 @@
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.06426985008328706</v>
+        <v>0.007781998869506921</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CF243</t>
+          <t>CF242</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -2080,7 +2074,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CF241</t>
+          <t>CF324</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2089,10 +2083,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>31.9</v>
       </c>
       <c r="I18" t="n">
-        <v>66.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
@@ -2101,31 +2095,31 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>70</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>117</v>
+        <v>122.19</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>10</v>
+        <v>2.26</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5.59</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0.59</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2153,13 +2147,13 @@
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.001896758002859728</v>
+        <v>0.06426985008328706</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CF244</t>
+          <t>CF243</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -2168,52 +2162,52 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CF631</t>
+          <t>CF241</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
-        <v>55.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="M19" t="n">
-        <v>34.56</v>
+        <v>117</v>
       </c>
       <c r="N19" t="n">
-        <v>3.68</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.74</v>
+        <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2222,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2241,13 +2235,13 @@
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>0.001896758002859728</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CF311</t>
+          <t>CF244</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -2256,52 +2250,52 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CF624</t>
+          <t>CF631</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CF311;CF523;CF624</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>51.6</v>
+        <v>37.5</v>
       </c>
       <c r="I20" t="n">
-        <v>48</v>
+        <v>55.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="L20" t="n">
-        <v>48.4</v>
+        <v>62.5</v>
       </c>
       <c r="M20" t="n">
-        <v>90.09</v>
+        <v>34.56</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>0.74</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2310,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2329,13 +2323,13 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.04401960784313726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CF312</t>
+          <t>CF311</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -2344,61 +2338,61 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CF123</t>
+          <t>CF624</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF311;CF523;CF624</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>52.3</v>
+        <v>51.6</v>
       </c>
       <c r="I21" t="n">
-        <v>44.7</v>
+        <v>48</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>47.7</v>
+        <v>48.4</v>
       </c>
       <c r="M21" t="n">
-        <v>135.98</v>
+        <v>90.09</v>
       </c>
       <c r="N21" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.29</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2417,13 +2411,13 @@
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.03062890062409986</v>
+        <v>0.04401960784313726</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF313</t>
+          <t>CF312</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -2432,61 +2426,61 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CF342</t>
+          <t>CF123</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>49</v>
+        <v>52.3</v>
       </c>
       <c r="I22" t="n">
-        <v>49.5</v>
+        <v>44.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>47.7</v>
       </c>
       <c r="M22" t="n">
-        <v>84.03999999999999</v>
+        <v>135.98</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="O22" t="n">
-        <v>0.91</v>
+        <v>3.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2505,13 +2499,13 @@
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.01831934759484695</v>
+        <v>0.03062890062409986</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CF316</t>
+          <t>CF313</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -2520,40 +2514,40 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CF612</t>
+          <t>CF342</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>40.2</v>
+        <v>49</v>
       </c>
       <c r="I23" t="n">
-        <v>57.1</v>
+        <v>49.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>59.8</v>
+        <v>51</v>
       </c>
       <c r="M23" t="n">
-        <v>91.97</v>
+        <v>84.03999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.55</v>
+        <v>0.91</v>
       </c>
       <c r="P23" t="n">
-        <v>5.84</v>
+        <v>2.68</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2562,19 +2556,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2593,101 +2587,99 @@
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.01079935405732741</v>
+        <v>0.01831934759484695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CF321</t>
+          <t>CF315</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>CF323</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Ouham-Pende</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
       <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Military Forces of the Central African Republic (2016-)</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Women (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Looting: On 30 December 2024, FACA soldiers demanded 5,000 CFA francs from a traveling young high school student in Mann (Kodi, Ngaoundaye, Ouham-Pende) after she was unable to produce her national identity card.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Ngaoundaye</t>
+        </is>
+      </c>
       <c r="AL24" t="n">
-        <v>0.08794444444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CF322</t>
+          <t>CF316</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -2696,7 +2688,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CF215</t>
+          <t>CF612</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2705,43 +2697,43 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>34.2</v>
+        <v>40.2</v>
       </c>
       <c r="I25" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="J25" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L25" t="n">
-        <v>65.8</v>
+        <v>59.8</v>
       </c>
       <c r="M25" t="n">
-        <v>137.58</v>
+        <v>91.97</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.49</v>
+        <v>4.55</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>5.84</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>21.11</v>
+        <v>5.41</v>
       </c>
       <c r="T25" t="n">
-        <v>0.49</v>
+        <v>4.55</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2750,64 +2742,32 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Ouham</t>
-        </is>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>Change to group/activity</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Group (Central African Republic)</t>
-        </is>
-      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Movement of forces: On 8 July 2025, an unidentified armed group occupied a primary school in Kouki (Nana-Bakassa, Ouham). Local sources say the armed group outnumbers security forces in the area.</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Nana-Bakassa</t>
-        </is>
-      </c>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>0.07166409282524312</v>
+        <v>0.01079935405732741</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CF323</t>
+          <t>CF321</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -2816,7 +2776,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CF612</t>
+          <t>CF323</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2825,43 +2785,43 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>32.4</v>
+        <v>46.4</v>
       </c>
       <c r="I26" t="n">
-        <v>62.1</v>
+        <v>50.7</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="K26" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="L26" t="n">
-        <v>67.59999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="M26" t="n">
-        <v>114.39</v>
+        <v>81.03</v>
       </c>
       <c r="N26" t="n">
-        <v>0.73</v>
+        <v>1.11</v>
       </c>
       <c r="O26" t="n">
-        <v>0.85</v>
+        <v>0.47</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>9.129999999999999</v>
+        <v>6.81</v>
       </c>
       <c r="T26" t="n">
-        <v>5.73</v>
+        <v>0.64</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2870,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4.75</v>
+        <v>0.93</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2889,13 +2849,13 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.1402223188225797</v>
+        <v>0.08794444444444445</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF324</t>
+          <t>CF322</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -2904,52 +2864,52 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CF333</t>
+          <t>CF215</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>30.2</v>
+        <v>34.2</v>
       </c>
       <c r="I27" t="n">
-        <v>66.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="J27" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L27" t="n">
-        <v>69.8</v>
+        <v>65.8</v>
       </c>
       <c r="M27" t="n">
-        <v>123.53</v>
+        <v>137.58</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.71</v>
+        <v>0.49</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>13.02</v>
+        <v>21.11</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2958,32 +2918,64 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Ouham</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Change to group/activity</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Central African Republic)</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Movement of forces: On 8 July 2025, an unidentified armed group occupied a primary school in Kouki (Nana-Bakassa, Ouham). Local sources say the armed group outnumbers security forces in the area.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Nana-Bakassa</t>
+        </is>
+      </c>
       <c r="AL27" t="n">
-        <v>0.1489729196224786</v>
+        <v>0.07166409282524312</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF331</t>
+          <t>CF323</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -2992,7 +2984,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF321</t>
+          <t>CF612</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3001,43 +2993,43 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>39.7</v>
+        <v>32.4</v>
       </c>
       <c r="I28" t="n">
-        <v>57.3</v>
+        <v>62.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="L28" t="n">
-        <v>60.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>60.11</v>
+        <v>114.39</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="P28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.85</v>
+        <v>9.129999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>7.69</v>
+        <v>5.73</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3046,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -3065,13 +3057,13 @@
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.235885770664328</v>
+        <v>0.1402223188225797</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CF332</t>
+          <t>CF324</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -3080,7 +3072,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF512</t>
+          <t>CF333</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3089,31 +3081,31 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.3</v>
+        <v>30.2</v>
       </c>
       <c r="I29" t="n">
-        <v>97</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>98.7</v>
+        <v>69.8</v>
       </c>
       <c r="M29" t="n">
-        <v>80.25</v>
+        <v>123.53</v>
       </c>
       <c r="N29" t="n">
-        <v>5.119999999999999</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0.96</v>
+        <v>1.71</v>
       </c>
       <c r="P29" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -3122,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -3153,13 +3145,13 @@
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.2684766214177979</v>
+        <v>0.1489729196224786</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CF333</t>
+          <t>CF331</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -3168,52 +3160,52 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CF324</t>
+          <t>CF321</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>41.7</v>
+        <v>39.7</v>
       </c>
       <c r="I30" t="n">
-        <v>56.2</v>
+        <v>57.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L30" t="n">
-        <v>58.3</v>
+        <v>60.3</v>
       </c>
       <c r="M30" t="n">
-        <v>161.3</v>
+        <v>60.11</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>13.15</v>
+        <v>3.85</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3222,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -3241,13 +3233,13 @@
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.1259439780966995</v>
+        <v>0.235885770664328</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CF334</t>
+          <t>CF332</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -3256,40 +3248,40 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CF635</t>
+          <t>CF512</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CF334;CF625;CF635</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="I31" t="n">
-        <v>96.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>96.8</v>
+        <v>98.7</v>
       </c>
       <c r="M31" t="n">
-        <v>98.83000000000001</v>
+        <v>80.25</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.119999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3310,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3329,13 +3321,13 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>0.2684766214177979</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CF341</t>
+          <t>CF333</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -3344,61 +3336,61 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CF433</t>
+          <t>CF324</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>52.7</v>
+        <v>41.7</v>
       </c>
       <c r="I32" t="n">
-        <v>40.8</v>
+        <v>56.2</v>
       </c>
       <c r="J32" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>47.3</v>
+        <v>58.3</v>
       </c>
       <c r="M32" t="n">
-        <v>78.81999999999999</v>
+        <v>161.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.57</v>
+        <v>13.15</v>
       </c>
       <c r="T32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3417,13 +3409,13 @@
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.002805119594614975</v>
+        <v>0.1259439780966995</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CF342</t>
+          <t>CF334</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -3432,43 +3424,43 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CF313</t>
+          <t>CF635</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF334;CF625;CF635</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>53.7</v>
+        <v>3.2</v>
       </c>
       <c r="I33" t="n">
-        <v>44.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>46.3</v>
+        <v>96.8</v>
       </c>
       <c r="M33" t="n">
-        <v>77.15000000000001</v>
+        <v>98.83000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3477,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3486,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3505,13 +3497,13 @@
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.006225308272476955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CF343</t>
+          <t>CF341</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -3520,7 +3512,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CF414</t>
+          <t>CF433</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3529,52 +3521,52 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>30</v>
+        <v>52.7</v>
       </c>
       <c r="I34" t="n">
-        <v>61.1</v>
+        <v>40.8</v>
       </c>
       <c r="J34" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="K34" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="L34" t="n">
-        <v>70</v>
+        <v>47.3</v>
       </c>
       <c r="M34" t="n">
-        <v>22.14</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>4.29</v>
+        <v>3.99</v>
       </c>
       <c r="O34" t="n">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="P34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.36</v>
+        <v>3.24</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="S34" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="T34" t="n">
-        <v>0.71</v>
+        <v>1.91</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3593,13 +3585,13 @@
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>0.002805119594614975</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CF344</t>
+          <t>CF342</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -3608,61 +3600,61 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CF126</t>
+          <t>CF313</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>32.3</v>
+        <v>53.7</v>
       </c>
       <c r="I35" t="n">
-        <v>63.4</v>
+        <v>44.7</v>
       </c>
       <c r="J35" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="K35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>67.7</v>
+        <v>46.3</v>
       </c>
       <c r="M35" t="n">
-        <v>25.38</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6</v>
+        <v>2.22</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3</v>
+        <v>1.43</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3681,13 +3673,13 @@
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>0.006225308272476955</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CF345</t>
+          <t>CF343</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -3696,7 +3688,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CF631</t>
+          <t>CF414</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3705,52 +3697,52 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="I36" t="n">
-        <v>57.3</v>
+        <v>61.1</v>
       </c>
       <c r="J36" t="n">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="L36" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="M36" t="n">
-        <v>26.59</v>
+        <v>22.14</v>
       </c>
       <c r="N36" t="n">
-        <v>0.37</v>
+        <v>4.29</v>
       </c>
       <c r="O36" t="n">
-        <v>1.12</v>
+        <v>0.36</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="T36" t="n">
-        <v>0.37</v>
+        <v>0.71</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.75</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3775,7 +3767,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CF411</t>
+          <t>CF344</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -3784,7 +3776,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CF433</t>
+          <t>CF126</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3793,31 +3785,31 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>60.6</v>
+        <v>32.3</v>
       </c>
       <c r="I37" t="n">
-        <v>35.1</v>
+        <v>63.4</v>
       </c>
       <c r="J37" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="L37" t="n">
-        <v>39.4</v>
+        <v>67.7</v>
       </c>
       <c r="M37" t="n">
-        <v>40.7</v>
+        <v>25.38</v>
       </c>
       <c r="N37" t="n">
-        <v>4.77</v>
+        <v>0.3</v>
       </c>
       <c r="O37" t="n">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3826,19 +3818,19 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="T37" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="U37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W37" t="n">
-        <v>2.5</v>
+        <v>1.51</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3857,13 +3849,13 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.02927391166190022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CF412</t>
+          <t>CF345</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -3872,7 +3864,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CF713</t>
+          <t>CF631</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3881,52 +3873,52 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>49.5</v>
+        <v>37.5</v>
       </c>
       <c r="I38" t="n">
-        <v>47.5</v>
+        <v>57.3</v>
       </c>
       <c r="J38" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L38" t="n">
-        <v>50.5</v>
+        <v>62.5</v>
       </c>
       <c r="M38" t="n">
-        <v>80.59999999999999</v>
+        <v>26.59</v>
       </c>
       <c r="N38" t="n">
-        <v>1.03</v>
+        <v>0.37</v>
       </c>
       <c r="O38" t="n">
-        <v>0.68</v>
+        <v>1.12</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="T38" t="n">
-        <v>0.68</v>
+        <v>0.37</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0.75</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3945,13 +3937,13 @@
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.1008684034736139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CF413</t>
+          <t>CF411</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -3960,40 +3952,40 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CF611</t>
+          <t>CF433</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>45.4</v>
+        <v>60.6</v>
       </c>
       <c r="I39" t="n">
-        <v>51.2</v>
+        <v>35.1</v>
       </c>
       <c r="J39" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
-        <v>54.6</v>
+        <v>39.4</v>
       </c>
       <c r="M39" t="n">
-        <v>99.84</v>
+        <v>40.7</v>
       </c>
       <c r="N39" t="n">
-        <v>12.8</v>
+        <v>4.77</v>
       </c>
       <c r="O39" t="n">
-        <v>3.77</v>
+        <v>0.29</v>
       </c>
       <c r="P39" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -4005,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0.76</v>
+        <v>0.59</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -4033,13 +4025,13 @@
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>0.0955909146119276</v>
+        <v>0.02927391166190022</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CF414</t>
+          <t>CF412</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -4048,7 +4040,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CF343</t>
+          <t>CF713</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4057,28 +4049,28 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>31.7</v>
+        <v>49.5</v>
       </c>
       <c r="I40" t="n">
-        <v>59</v>
+        <v>47.5</v>
       </c>
       <c r="J40" t="n">
-        <v>8.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="K40" t="n">
         <v>0.9</v>
       </c>
       <c r="L40" t="n">
-        <v>68.3</v>
+        <v>50.5</v>
       </c>
       <c r="M40" t="n">
-        <v>78.39</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>16.37</v>
+        <v>1.03</v>
       </c>
       <c r="O40" t="n">
-        <v>2.18</v>
+        <v>0.68</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -4090,19 +4082,19 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>7.53</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -4121,13 +4113,13 @@
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.08223110837690967</v>
+        <v>0.1008684034736139</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CF421</t>
+          <t>CF413</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -4136,61 +4128,61 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CF533</t>
+          <t>CF611</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>44.6</v>
+        <v>45.4</v>
       </c>
       <c r="I41" t="n">
-        <v>50.5</v>
+        <v>51.2</v>
       </c>
       <c r="J41" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>55.4</v>
+        <v>54.6</v>
       </c>
       <c r="M41" t="n">
-        <v>77.48999999999999</v>
+        <v>99.84</v>
       </c>
       <c r="N41" t="n">
-        <v>3.66</v>
+        <v>12.8</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8200000000000001</v>
+        <v>3.77</v>
       </c>
       <c r="P41" t="n">
-        <v>1.32</v>
+        <v>0.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>0.76</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>6.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -4209,13 +4201,13 @@
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.04567757763574149</v>
+        <v>0.0955909146119276</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CF422</t>
+          <t>CF414</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -4224,7 +4216,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF126</t>
+          <t>CF343</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4233,28 +4225,28 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>37.3</v>
+        <v>31.7</v>
       </c>
       <c r="I42" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="J42" t="n">
-        <v>2.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="L42" t="n">
-        <v>62.7</v>
+        <v>68.3</v>
       </c>
       <c r="M42" t="n">
-        <v>54.11</v>
+        <v>78.39</v>
       </c>
       <c r="N42" t="n">
-        <v>4.44</v>
+        <v>16.37</v>
       </c>
       <c r="O42" t="n">
-        <v>1.18</v>
+        <v>2.18</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -4266,19 +4258,19 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.93</v>
+        <v>0.38</v>
       </c>
       <c r="T42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W42" t="n">
-        <v>8.9</v>
+        <v>7.53</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -4297,13 +4289,13 @@
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="n">
-        <v>0.06886746653720785</v>
+        <v>0.08223110837690967</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CF423</t>
+          <t>CF421</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -4312,61 +4304,61 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CF313</t>
+          <t>CF533</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>50.9</v>
+        <v>44.6</v>
       </c>
       <c r="I43" t="n">
-        <v>48</v>
+        <v>50.5</v>
       </c>
       <c r="J43" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L43" t="n">
-        <v>49.1</v>
+        <v>55.4</v>
       </c>
       <c r="M43" t="n">
-        <v>27.34</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>0.32</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.32</v>
+        <v>3.44</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>0.38</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>0.44</v>
       </c>
       <c r="T43" t="n">
-        <v>0.32</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>6.779999999999999</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -4385,13 +4377,13 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>0.04567757763574149</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CF431</t>
+          <t>CF422</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -4400,7 +4392,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CF216</t>
+          <t>CF126</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4409,52 +4401,52 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>53.7</v>
+        <v>37.3</v>
       </c>
       <c r="I44" t="n">
-        <v>37</v>
+        <v>58.3</v>
       </c>
       <c r="J44" t="n">
-        <v>9.1</v>
+        <v>2.9</v>
       </c>
       <c r="K44" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="L44" t="n">
-        <v>46.3</v>
+        <v>62.7</v>
       </c>
       <c r="M44" t="n">
-        <v>68.43000000000001</v>
+        <v>54.11</v>
       </c>
       <c r="N44" t="n">
-        <v>26.62</v>
+        <v>4.44</v>
       </c>
       <c r="O44" t="n">
-        <v>2.16</v>
+        <v>1.18</v>
       </c>
       <c r="P44" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="T44" t="n">
-        <v>0.96</v>
+        <v>1.86</v>
       </c>
       <c r="U44" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.43</v>
+        <v>8.9</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -4473,13 +4465,13 @@
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.08920355615004094</v>
+        <v>0.06886746653720785</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CF432</t>
+          <t>CF423</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -4488,61 +4480,61 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CF631</t>
+          <t>CF313</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>21.4</v>
+        <v>50.9</v>
       </c>
       <c r="I45" t="n">
-        <v>69.40000000000001</v>
+        <v>48</v>
       </c>
       <c r="J45" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="K45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>78.59999999999999</v>
+        <v>49.1</v>
       </c>
       <c r="M45" t="n">
-        <v>120.71</v>
+        <v>27.34</v>
       </c>
       <c r="N45" t="n">
-        <v>45.36</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="R45" t="n">
-        <v>0.42</v>
+        <v>4</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
-        <v>0.42</v>
+        <v>0.32</v>
       </c>
       <c r="U45" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4561,13 +4553,13 @@
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.02063871388225071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CF433</t>
+          <t>CF431</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -4576,7 +4568,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CF411</t>
+          <t>CF216</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4585,52 +4577,52 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>35.6</v>
+        <v>53.7</v>
       </c>
       <c r="I46" t="n">
-        <v>54.8</v>
+        <v>37</v>
       </c>
       <c r="J46" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="K46" t="n">
         <v>0.3</v>
       </c>
       <c r="L46" t="n">
-        <v>64.40000000000001</v>
+        <v>46.3</v>
       </c>
       <c r="M46" t="n">
-        <v>35.12</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>14.68</v>
+        <v>26.62</v>
       </c>
       <c r="O46" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
         <v>0.96</v>
       </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W46" t="n">
-        <v>0.32</v>
+        <v>1.43</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4649,13 +4641,13 @@
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>0.08920355615004094</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CF434</t>
+          <t>CF432</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -4664,61 +4656,61 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CF224</t>
+          <t>CF631</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>31.8</v>
+        <v>21.4</v>
       </c>
       <c r="I47" t="n">
-        <v>63.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L47" t="n">
-        <v>68.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>133.27</v>
+        <v>120.71</v>
       </c>
       <c r="N47" t="n">
-        <v>3.71</v>
+        <v>45.36</v>
       </c>
       <c r="O47" t="n">
-        <v>2.27</v>
+        <v>1.26</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.9</v>
+        <v>0.42</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="U47" t="n">
-        <v>0.48</v>
+        <v>5.88</v>
       </c>
       <c r="V47" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -4737,13 +4729,13 @@
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.02145505097312326</v>
+        <v>0.02063871388225071</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CF435</t>
+          <t>CF433</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -4752,7 +4744,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CF621</t>
+          <t>CF411</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4761,52 +4753,52 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="I48" t="n">
-        <v>56.2</v>
+        <v>54.8</v>
       </c>
       <c r="J48" t="n">
-        <v>4.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="L48" t="n">
-        <v>64.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>105.84</v>
+        <v>35.12</v>
       </c>
       <c r="N48" t="n">
-        <v>1.2</v>
+        <v>14.68</v>
       </c>
       <c r="O48" t="n">
-        <v>5.42</v>
+        <v>0.96</v>
       </c>
       <c r="P48" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.39</v>
+        <v>0.32</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>8.49</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>12.34</v>
+        <v>0.32</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
@@ -4825,13 +4817,13 @@
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.2338077992082877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CF511</t>
+          <t>CF434</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -4840,61 +4832,61 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CF521</t>
+          <t>CF224</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>36.7</v>
+        <v>31.8</v>
       </c>
       <c r="I49" t="n">
-        <v>61.1</v>
+        <v>63.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="K49" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>63.3</v>
+        <v>68.2</v>
       </c>
       <c r="M49" t="n">
-        <v>49.08</v>
+        <v>133.27</v>
       </c>
       <c r="N49" t="n">
-        <v>0.39</v>
+        <v>3.71</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9</v>
+        <v>2.27</v>
       </c>
       <c r="P49" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.39</v>
+        <v>1.9</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>4</v>
+        <v>0.48</v>
       </c>
       <c r="U49" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="W49" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -4913,13 +4905,13 @@
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.07733553309960817</v>
+        <v>0.02145505097312326</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CF512</t>
+          <t>CF435</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -4928,61 +4920,61 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CF242</t>
+          <t>CF621</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>41.1</v>
+        <v>35.8</v>
       </c>
       <c r="I50" t="n">
-        <v>56.9</v>
+        <v>56.2</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L50" t="n">
-        <v>58.9</v>
+        <v>64.2</v>
       </c>
       <c r="M50" t="n">
-        <v>55.26000000000001</v>
+        <v>105.84</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>5.77</v>
+        <v>0.37</v>
       </c>
       <c r="T50" t="n">
-        <v>0.82</v>
+        <v>8.49</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>12.34</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -5001,13 +4993,13 @@
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="n">
-        <v>0.04488718194911186</v>
+        <v>0.2338077992082877</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CF521</t>
+          <t>CF511</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -5016,7 +5008,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CF432</t>
+          <t>CF521</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5025,52 +5017,52 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>40.3</v>
+        <v>36.7</v>
       </c>
       <c r="I51" t="n">
-        <v>54.7</v>
+        <v>61.1</v>
       </c>
       <c r="J51" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="L51" t="n">
-        <v>59.7</v>
+        <v>63.3</v>
       </c>
       <c r="M51" t="n">
-        <v>56.94</v>
+        <v>49.08</v>
       </c>
       <c r="N51" t="n">
-        <v>4.65</v>
+        <v>0.39</v>
       </c>
       <c r="O51" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.87</v>
+        <v>0.39</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="T51" t="n">
-        <v>0.35</v>
+        <v>4</v>
       </c>
       <c r="U51" t="n">
-        <v>3.62</v>
+        <v>0.4</v>
       </c>
       <c r="V51" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>3.52</v>
+        <v>1.68</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -5089,13 +5081,13 @@
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.09620795926571084</v>
+        <v>0.07733553309960817</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CF522</t>
+          <t>CF512</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -5104,61 +5096,61 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF216</t>
+          <t>CF242</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>23.2</v>
+        <v>41.1</v>
       </c>
       <c r="I52" t="n">
-        <v>57.1</v>
+        <v>56.9</v>
       </c>
       <c r="J52" t="n">
-        <v>17.3</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>76.8</v>
+        <v>58.9</v>
       </c>
       <c r="M52" t="n">
-        <v>63.6</v>
+        <v>55.26000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>23.97</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.92</v>
+        <v>5.77</v>
       </c>
       <c r="T52" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="U52" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>7.82</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -5177,13 +5169,13 @@
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.1257285595337219</v>
+        <v>0.04488718194911186</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CF523</t>
+          <t>CF521</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -5192,61 +5184,61 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CF624</t>
+          <t>CF432</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CF311;CF523;CF624</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>7.4</v>
+        <v>40.3</v>
       </c>
       <c r="I53" t="n">
-        <v>89.7</v>
+        <v>54.7</v>
       </c>
       <c r="J53" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="K53" t="n">
         <v>0.6</v>
       </c>
       <c r="L53" t="n">
-        <v>92.59999999999999</v>
+        <v>59.7</v>
       </c>
       <c r="M53" t="n">
-        <v>79.66</v>
+        <v>56.94</v>
       </c>
       <c r="N53" t="n">
-        <v>0.58</v>
+        <v>4.65</v>
       </c>
       <c r="O53" t="n">
-        <v>0.58</v>
+        <v>1.08</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U53" t="n">
-        <v>1.16</v>
+        <v>3.62</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W53" t="n">
-        <v>0.58</v>
+        <v>3.52</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -5265,13 +5257,13 @@
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.01002004008016032</v>
+        <v>0.09620795926571084</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CF524</t>
+          <t>CF522</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -5280,7 +5272,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CF123</t>
+          <t>CF216</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5289,52 +5281,52 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>36</v>
+        <v>23.2</v>
       </c>
       <c r="I54" t="n">
-        <v>59.8</v>
+        <v>57.1</v>
       </c>
       <c r="J54" t="n">
-        <v>3.9</v>
+        <v>17.3</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="L54" t="n">
-        <v>64</v>
+        <v>76.8</v>
       </c>
       <c r="M54" t="n">
-        <v>32.13</v>
+        <v>63.6</v>
       </c>
       <c r="N54" t="n">
-        <v>0.9</v>
+        <v>23.97</v>
       </c>
       <c r="O54" t="n">
-        <v>0.6</v>
+        <v>4.93</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.6</v>
+        <v>1.89</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S54" t="n">
-        <v>0.6</v>
+        <v>3.92</v>
       </c>
       <c r="T54" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54" t="n">
-        <v>0.3</v>
+        <v>7.82</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
@@ -5353,13 +5345,13 @@
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>0.1257285595337219</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CF531</t>
+          <t>CF523</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -5368,130 +5360,86 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CF312</t>
+          <t>CF624</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF311;CF523;CF624</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>43.2</v>
+        <v>7.4</v>
       </c>
       <c r="I55" t="n">
-        <v>52.5</v>
+        <v>89.7</v>
       </c>
       <c r="J55" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="K55" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="L55" t="n">
-        <v>56.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>158.21</v>
+        <v>79.66</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="O55" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="P55" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="V55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.58</v>
+        <v>0.58</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Vakaga</t>
-        </is>
-      </c>
-      <c r="Z55" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>3</v>
-      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Violence against civilians ---- Violence against civilians ---- Strategic developments</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>Attack ---- Attack ---- Other</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Group (Central African Republic) ---- Unidentified Armed Group (Sudan) ---- Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>Refugees/IDPs (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic) ---- Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Civilians (Chad); Labor Group (Central African Republic); Labor Group (Chad); Muslim Group (Central African Republic); Muslim Group (Chad); Students (Central African Republic); Students (Chad) ---- Students (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>On 22 March 2025, an unidentified armed group ambushed and attacked traveling traders, and children from the Central African Republic and Chad, 12 kilometers from Boromata, closest to Keche (Ouandja, Birao, Central African Republic). 2 children were killed and three others went missing. The children were traveling to attend Koranic schools. ---- On 11 July 2025, an unidentified armed group from Sudan attacked and killed 2 civilians, including a student in Am-Dafock (Ridina, Birao, Vakaga). ---- Displacement: Around 16 July 2025 (as reported), hundreds of civilians from Zaire, Kafao and Bachama (coded separately) arrived in Birao (Ridina, Birao, Vakaga), after fleeing violence. Many are sheltering in schools and face shortages of food and medicine.</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>2025-03-22 ---- 2025-07-11 ---- 2025-07-16</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Birao</t>
-        </is>
-      </c>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.03731224033237456</v>
+        <v>0.01002004008016032</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CF533</t>
+          <t>CF524</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -5500,7 +5448,7 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CF421</t>
+          <t>CF123</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5509,52 +5457,52 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>38.8</v>
+        <v>36</v>
       </c>
       <c r="I56" t="n">
-        <v>53.7</v>
+        <v>59.8</v>
       </c>
       <c r="J56" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L56" t="n">
-        <v>61.2</v>
+        <v>64</v>
       </c>
       <c r="M56" t="n">
-        <v>22.89</v>
+        <v>32.13</v>
       </c>
       <c r="N56" t="n">
-        <v>4.48</v>
+        <v>0.9</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P56" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T56" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -5579,7 +5527,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CF611</t>
+          <t>CF531</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -5588,86 +5536,130 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CF714</t>
+          <t>CF312</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>42.6</v>
+        <v>43.2</v>
       </c>
       <c r="I57" t="n">
-        <v>54.3</v>
+        <v>52.5</v>
       </c>
       <c r="J57" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L57" t="n">
-        <v>57.4</v>
+        <v>56.8</v>
       </c>
       <c r="M57" t="n">
-        <v>87.95</v>
+        <v>158.21</v>
       </c>
       <c r="N57" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.63</v>
+        <v>0.31</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.48</v>
+        <v>2.65</v>
       </c>
       <c r="T57" t="n">
-        <v>0.48</v>
+        <v>18</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V57" t="n">
-        <v>0.96</v>
+        <v>1.83</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Vakaga</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>3</v>
+      </c>
       <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack ---- Other</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Central African Republic) ---- Unidentified Armed Group (Sudan) ---- Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic) ---- Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Civilians (Chad); Labor Group (Central African Republic); Labor Group (Chad); Muslim Group (Central African Republic); Muslim Group (Chad); Students (Central African Republic); Students (Chad) ---- Students (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>On 22 March 2025, an unidentified armed group ambushed and attacked traveling traders, and children from the Central African Republic and Chad, 12 kilometers from Boromata, closest to Keche (Ouandja, Birao, Central African Republic). 2 children were killed and three others went missing. The children were traveling to attend Koranic schools. ---- On 11 July 2025, an unidentified armed group from Sudan attacked and killed 2 civilians, including a student in Am-Dafock (Ridina, Birao, Vakaga). ---- Displacement: Around 16 July 2025 (as reported), hundreds of civilians from Zaire, Kafao and Bachama (coded separately) arrived in Birao (Ridina, Birao, Vakaga), after fleeing violence. Many are sheltering in schools and face shortages of food and medicine.</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>2025-03-22 ---- 2025-07-11 ---- 2025-07-16</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Birao</t>
+        </is>
+      </c>
       <c r="AL57" t="n">
-        <v>0.05569103212826922</v>
+        <v>0.03731224033237456</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CF612</t>
+          <t>CF533</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -5676,7 +5668,7 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CF316</t>
+          <t>CF421</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5685,52 +5677,52 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>47.9</v>
+        <v>38.8</v>
       </c>
       <c r="I58" t="n">
-        <v>49.7</v>
+        <v>53.7</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L58" t="n">
-        <v>52.1</v>
+        <v>61.2</v>
       </c>
       <c r="M58" t="n">
-        <v>122.14</v>
+        <v>22.89</v>
       </c>
       <c r="N58" t="n">
-        <v>0.83</v>
+        <v>4.48</v>
       </c>
       <c r="O58" t="n">
-        <v>2.72</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="U58" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W58" t="n">
-        <v>1.64</v>
+        <v>0.5</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
@@ -5749,13 +5741,13 @@
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.01297359585162816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CF613</t>
+          <t>CF611</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -5764,37 +5756,37 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CF126</t>
+          <t>CF714</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>23.3</v>
+        <v>42.6</v>
       </c>
       <c r="I59" t="n">
-        <v>69.8</v>
+        <v>54.3</v>
       </c>
       <c r="J59" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>76.7</v>
+        <v>57.4</v>
       </c>
       <c r="M59" t="n">
-        <v>101.19</v>
+        <v>87.95</v>
       </c>
       <c r="N59" t="n">
-        <v>5.15</v>
+        <v>0.48</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5806,19 +5798,19 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="W59" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -5837,13 +5829,13 @@
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>0.007228785671899445</v>
+        <v>0.05569103212826922</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CF615</t>
+          <t>CF612</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -5852,7 +5844,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CF124</t>
+          <t>CF316</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5861,52 +5853,52 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>17.7</v>
+        <v>47.9</v>
       </c>
       <c r="I60" t="n">
-        <v>50.8</v>
+        <v>49.7</v>
       </c>
       <c r="J60" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>28.6</v>
+        <v>0.4</v>
       </c>
       <c r="L60" t="n">
-        <v>82.3</v>
+        <v>52.1</v>
       </c>
       <c r="M60" t="n">
-        <v>138.38</v>
+        <v>122.14</v>
       </c>
       <c r="N60" t="n">
-        <v>3.58</v>
+        <v>0.83</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U60" t="n">
-        <v>1.95</v>
+        <v>0.71</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>90.63</v>
+        <v>1.64</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -5925,13 +5917,13 @@
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.2452212173062821</v>
+        <v>0.01297359585162816</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CF616</t>
+          <t>CF613</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -5940,7 +5932,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CF414</t>
+          <t>CF126</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5949,25 +5941,25 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>13.6</v>
+        <v>23.3</v>
       </c>
       <c r="I61" t="n">
-        <v>65.5</v>
+        <v>69.8</v>
       </c>
       <c r="J61" t="n">
-        <v>18.7</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="L61" t="n">
-        <v>86.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="M61" t="n">
-        <v>129.27</v>
+        <v>101.19</v>
       </c>
       <c r="N61" t="n">
-        <v>45.34</v>
+        <v>5.15</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -5979,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -5994,76 +5986,32 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
       </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Basse-Kotto</t>
-        </is>
-      </c>
-      <c r="Z61" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Riots</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>Mob violence</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>Rioters (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>Langbachi Communal Group (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>Rioters (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Yakoma Communal Group (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>On 31 October 2024, Langbachi and Yakoma communities clashed in Satema (Kotto-Oubangui, Satema, Basse-Kotto) after a Yakoma student stabbed his Langbachi classmate. Unspecified fatalities, coded as 3. The clashes caused villagers to flee to the Democratic Republic of Congo.</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Satema</t>
-        </is>
-      </c>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.005959954463269269</v>
+        <v>0.007228785671899445</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CF621</t>
+          <t>CF615</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -6072,7 +6020,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CF623</t>
+          <t>CF124</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6081,34 +6029,34 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>35.8</v>
+        <v>17.7</v>
       </c>
       <c r="I62" t="n">
-        <v>56.5</v>
+        <v>50.8</v>
       </c>
       <c r="J62" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="K62" t="n">
-        <v>3.1</v>
+        <v>28.6</v>
       </c>
       <c r="L62" t="n">
-        <v>64.2</v>
+        <v>82.3</v>
       </c>
       <c r="M62" t="n">
-        <v>125.01</v>
+        <v>138.38</v>
       </c>
       <c r="N62" t="n">
-        <v>14.7</v>
+        <v>3.58</v>
       </c>
       <c r="O62" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -6120,13 +6068,13 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>5.36</v>
+        <v>90.63</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
@@ -6145,13 +6093,13 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.01696122512576237</v>
+        <v>0.2452212173062821</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CF622</t>
+          <t>CF616</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -6160,7 +6108,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CF623</t>
+          <t>CF414</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6169,28 +6117,28 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>22.9</v>
+        <v>13.6</v>
       </c>
       <c r="I63" t="n">
-        <v>55</v>
+        <v>65.5</v>
       </c>
       <c r="J63" t="n">
-        <v>12.9</v>
+        <v>18.7</v>
       </c>
       <c r="K63" t="n">
-        <v>9.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="L63" t="n">
-        <v>77.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>57.06999999999999</v>
+        <v>129.27</v>
       </c>
       <c r="N63" t="n">
-        <v>30.89</v>
+        <v>45.34</v>
       </c>
       <c r="O63" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -6199,47 +6147,91 @@
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>9.220000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
       </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Basse-Kotto</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
       <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Mob violence</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>Rioters (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Langbachi Communal Group (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>Rioters (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Yakoma Communal Group (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>On 31 October 2024, Langbachi and Yakoma communities clashed in Satema (Kotto-Oubangui, Satema, Basse-Kotto) after a Yakoma student stabbed his Langbachi classmate. Unspecified fatalities, coded as 3. The clashes caused villagers to flee to the Democratic Republic of Congo.</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Satema</t>
+        </is>
+      </c>
       <c r="AL63" t="n">
-        <v>0.001482673896467</v>
+        <v>0.005959954463269269</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CF623</t>
+          <t>CF621</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -6248,7 +6240,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CF622</t>
+          <t>CF623</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6257,40 +6249,40 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>13.7</v>
+        <v>35.8</v>
       </c>
       <c r="I64" t="n">
-        <v>65.40000000000001</v>
+        <v>56.5</v>
       </c>
       <c r="J64" t="n">
-        <v>10.8</v>
+        <v>4.7</v>
       </c>
       <c r="K64" t="n">
-        <v>10.2</v>
+        <v>3.1</v>
       </c>
       <c r="L64" t="n">
-        <v>86.3</v>
+        <v>64.2</v>
       </c>
       <c r="M64" t="n">
-        <v>65.2</v>
+        <v>125.01</v>
       </c>
       <c r="N64" t="n">
-        <v>25.37</v>
+        <v>14.7</v>
       </c>
       <c r="O64" t="n">
-        <v>4.39</v>
+        <v>0.31</v>
       </c>
       <c r="P64" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -6299,10 +6291,10 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>35.9</v>
+        <v>5.36</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -6321,13 +6313,13 @@
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.0171003717472119</v>
+        <v>0.01696122512576237</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CF624</t>
+          <t>CF622</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -6336,37 +6328,37 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CF523</t>
+          <t>CF623</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CF311;CF523;CF624</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>43.1</v>
+        <v>22.9</v>
       </c>
       <c r="I65" t="n">
-        <v>55.6</v>
+        <v>55</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9</v>
+        <v>12.9</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>56.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>68.33</v>
+        <v>57.06999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>30.89</v>
       </c>
       <c r="O65" t="n">
-        <v>3.93</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -6381,16 +6373,16 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W65" t="n">
-        <v>0.4</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -6409,13 +6401,13 @@
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.06298328760289348</v>
+        <v>0.001482673896467</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CF625</t>
+          <t>CF623</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -6424,40 +6416,40 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CF635</t>
+          <t>CF622</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CF334;CF625;CF635</t>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>37.5</v>
+        <v>13.7</v>
       </c>
       <c r="I66" t="n">
-        <v>62.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="L66" t="n">
-        <v>62.5</v>
+        <v>86.3</v>
       </c>
       <c r="M66" t="n">
-        <v>8.33</v>
+        <v>65.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>25.37</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -6466,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T66" t="n">
         <v>0</v>
@@ -6475,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>35.9</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -6497,13 +6489,13 @@
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0</v>
+        <v>0.0171003717472119</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CF631</t>
+          <t>CF624</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -6512,37 +6504,37 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CF432</t>
+          <t>CF523</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF311;CF523;CF624</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>41.8</v>
+        <v>43.1</v>
       </c>
       <c r="I67" t="n">
-        <v>53</v>
+        <v>55.6</v>
       </c>
       <c r="J67" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="K67" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="L67" t="n">
-        <v>58.2</v>
+        <v>56.9</v>
       </c>
       <c r="M67" t="n">
-        <v>72.88</v>
+        <v>68.33</v>
       </c>
       <c r="N67" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -6551,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -6560,78 +6552,38 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>3.51</v>
+        <v>0.4</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
       </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>Haut-Mbomou</t>
-        </is>
-      </c>
-      <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>Azande Ani Kpi Gbe (Central African Republic)</t>
-        </is>
-      </c>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Labor Group (Central African Republic); Students (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Non-violent activity: Around 28 January 2025 (as reported), Azande Ani Kpi Gbe militia prohibited (means not specified) civilians from continuing their commercial activities and attending school in Obo (Obo, Obo, Haut-Mbomou) after the arrest of some of their colleagues who had been involved in an attack against civilians (coded separately).</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>2025-01-28</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Obo</t>
-        </is>
-      </c>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.1739807033924681</v>
+        <v>0.06298328760289348</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CF632</t>
+          <t>CF625</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -6640,31 +6592,31 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CF224</t>
+          <t>CF635</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+          <t>CF334;CF625;CF635</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>9.5</v>
+        <v>37.5</v>
       </c>
       <c r="I68" t="n">
-        <v>81</v>
+        <v>62.5</v>
       </c>
       <c r="J68" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>90.5</v>
+        <v>62.5</v>
       </c>
       <c r="M68" t="n">
-        <v>203.59</v>
+        <v>8.33</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -6682,19 +6634,19 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>44.52</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
         <v>0</v>
@@ -6713,13 +6665,13 @@
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CF633</t>
+          <t>CF631</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -6728,7 +6680,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CF215</t>
+          <t>CF432</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6737,52 +6689,52 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>51.7</v>
+        <v>41.8</v>
       </c>
       <c r="I69" t="n">
-        <v>42.1</v>
+        <v>53</v>
       </c>
       <c r="J69" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="L69" t="n">
-        <v>48.3</v>
+        <v>58.2</v>
       </c>
       <c r="M69" t="n">
-        <v>83.83</v>
+        <v>72.88</v>
       </c>
       <c r="N69" t="n">
-        <v>17.12</v>
+        <v>6.92</v>
       </c>
       <c r="O69" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S69" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.65</v>
+        <v>6.06</v>
       </c>
       <c r="V69" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="W69" t="n">
-        <v>1.25</v>
+        <v>3.51</v>
       </c>
       <c r="X69" t="n">
         <v>0</v>
@@ -6806,12 +6758,12 @@
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>Looting/property destruction</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>UPC: Union for Peace in the Central African Republic</t>
+          <t>Azande Ani Kpi Gbe (Central African Republic)</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr"/>
@@ -6822,32 +6774,32 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Government of the Central African Republic (2016-)</t>
+          <t>Labor Group (Central African Republic); Students (Central African Republic)</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Looting: On 18 February 2024, suspected UPC militants looted from delegates of the Ministry of Education between Zemio and Djema, coded to Zemio (Zemio, Zemio, Haut-Mbomou). The delegates were on a mission to assess sites for the construction of a secondary school.</t>
+          <t>Non-violent activity: Around 28 January 2025 (as reported), Azande Ani Kpi Gbe militia prohibited (means not specified) civilians from continuing their commercial activities and attending school in Obo (Obo, Obo, Haut-Mbomou) after the arrest of some of their colleagues who had been involved in an attack against civilians (coded separately).</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Zemio</t>
+          <t>Obo</t>
         </is>
       </c>
       <c r="AL69" t="n">
-        <v>0.2224537037037037</v>
+        <v>0.1739807033924681</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CF634</t>
+          <t>CF632</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -6856,31 +6808,31 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CF435</t>
+          <t>CF224</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>20.9</v>
+        <v>9.5</v>
       </c>
       <c r="I70" t="n">
-        <v>59.4</v>
+        <v>81</v>
       </c>
       <c r="J70" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="K70" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>79.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="M70" t="n">
-        <v>74.14999999999999</v>
+        <v>203.59</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -6892,25 +6844,25 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>14.29</v>
+        <v>44.52</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="W70" t="n">
-        <v>63.95</v>
+        <v>5.49</v>
       </c>
       <c r="X70" t="n">
         <v>0</v>
@@ -6929,13 +6881,13 @@
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.1051188299817185</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CF635</t>
+          <t>CF633</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -6944,76 +6896,126 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CF625</t>
+          <t>CF215</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CF334;CF625;CF635</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I71" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L71" t="n">
+        <v>48.3</v>
+      </c>
       <c r="M71" t="n">
-        <v>44.3</v>
+        <v>83.83</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>17.12</v>
       </c>
       <c r="O71" t="n">
-        <v>0.33</v>
+        <v>2.11</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V71" t="n">
-        <v>1.3</v>
+        <v>0.85</v>
       </c>
       <c r="W71" t="n">
-        <v>14.01</v>
+        <v>1.25</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
       </c>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Haut-Mbomou</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1</v>
+      </c>
       <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr"/>
-      <c r="AE71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Looting/property destruction</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>UPC: Union for Peace in the Central African Republic</t>
+        </is>
+      </c>
       <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
-      <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Government of the Central African Republic (2016-)</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Looting: On 18 February 2024, suspected UPC militants looted from delegates of the Ministry of Education between Zemio and Djema, coded to Zemio (Zemio, Zemio, Haut-Mbomou). The delegates were on a mission to assess sites for the construction of a secondary school.</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Zemio</t>
+        </is>
+      </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>0.2224537037037037</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CF711</t>
+          <t>CF634</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -7022,7 +7024,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CF414</t>
+          <t>CF435</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7031,34 +7033,34 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>77.09999999999999</v>
+        <v>20.9</v>
       </c>
       <c r="I72" t="n">
-        <v>19.6</v>
+        <v>59.4</v>
       </c>
       <c r="J72" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="K72" t="n">
-        <v>0.1</v>
+        <v>18.1</v>
       </c>
       <c r="L72" t="n">
-        <v>22.9</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="M72" t="n">
-        <v>51.54</v>
+        <v>74.14999999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.76</v>
+        <v>2.17</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -7067,85 +7069,41 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>0.67</v>
+        <v>63.95</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
       </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Bangui</t>
-        </is>
-      </c>
-      <c r="Z72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>6</v>
-      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Violence against civilians ---- Protests ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Protests</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>Attack ---- Peaceful protest ---- Excessive force against protesters ---- Attack ---- Attack ---- Peaceful protest</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>Military Forces of the Central African Republic (2016-) ---- Protesters (Central African Republic) ---- Protesters (Central African Republic) ---- Military Forces of the Central African Republic (2016-) ---- Unidentified Armed Group (Central African Republic) ---- Protesters (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>Students (Central African Republic) ---- Students (Central African Republic) ---- Teachers (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>Civilians (Central African Republic) ---- Police Forces of the Central African Republic (2016-) ---- Civilians (Central African Republic) ---- Civilians (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Students (Central African Republic) ---- Students (Central African Republic); Taxi Drivers (Central African Republic) ---- Private Security Forces (Central African Republic)</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>On 18 December 2024, a FACA soldier shot and injured a female student near the Avenir School Complex at the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui). The shooting occurred when the FACA forces arrested one civilian and slapped another who retaliated during security checks. The injured student was taken to a community hospital for treatment. ---- On 18 December 2024, students from Avenir School Complex protested near the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui), condemning the shooting of a fellow student by a FACA soldier (coded separately). The protesters demanded accountability and sanctions against the soldier, criticizing the use of firearms during regular security checks. ---- On 11 February 2025, Gbaloko high school students protested in Bangui (Arrondissement 1, Bangui), to condemn an alleged extortion scheme by the school administration, where exams, assignments, and lessons have allegedly become opportunities for financial exploitation. Police fired live ammunition to suppress protesters. ---- On 25 April 2025, FACA soldiers attacked a student working as a commercial motorbike driver (taxi) in Bangui - 3 (Arrondissement 3, Bangui, Bangui). They punched and kicked him until he collapsed, and left him unconscious on the side of a road. They also looted his mobile phone and motorbike. There were no fatalities. The victim spent two days in a coma. ---- On 30 May 2025, an unidentified armed group attacked the AMA scientific high school in the Kokpa neighborhood in Bangui - 4 (Arrondissement 4, Bangui, Bangui), torturing the security guard (was armed only with a baton), who later died. The attackers looted exam papers, equipment, and vandalized offices. ---- On 14 July 2025, a dozen of contractual teachers protested outside the administrative building in Bangui (Arrondissement 1, Bangui, Bangui), to demand three months of unpaid salaries and denounce unequal payments and lack of support for deployment.</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>2024-12-18 ---- 2024-12-18 ---- 2025-02-11 ---- 2025-04-25 ---- 2025-05-30 ---- 2025-07-14</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Bangui</t>
-        </is>
-      </c>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.1481596371688042</v>
+        <v>0.1051188299817185</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CF712</t>
+          <t>CF635</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -7154,37 +7112,27 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CF413</t>
+          <t>CF625</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>61</v>
-      </c>
-      <c r="I73" t="n">
-        <v>34</v>
-      </c>
-      <c r="J73" t="n">
-        <v>5</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>39</v>
-      </c>
+          <t>CF334;CF625;CF635</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>16.31</v>
+        <v>44.3</v>
       </c>
       <c r="N73" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -7196,19 +7144,19 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="T73" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>14.01</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -7227,13 +7175,13 @@
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>0.02227003293084523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CF713</t>
+          <t>CF711</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -7242,7 +7190,7 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CF412</t>
+          <t>CF414</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -7251,43 +7199,43 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>54.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>43.6</v>
+        <v>19.6</v>
       </c>
       <c r="J74" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L74" t="n">
-        <v>45.7</v>
+        <v>22.9</v>
       </c>
       <c r="M74" t="n">
-        <v>91.02</v>
+        <v>51.54</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O74" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.38</v>
+        <v>0.76</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -7296,32 +7244,76 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="X74" t="n">
         <v>0</v>
       </c>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Bangui</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>6</v>
+      </c>
       <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
-      <c r="AJ74" t="inlineStr"/>
-      <c r="AK74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Protests ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Protests</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Attack ---- Peaceful protest ---- Excessive force against protesters ---- Attack ---- Attack ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>Military Forces of the Central African Republic (2016-) ---- Protesters (Central African Republic) ---- Protesters (Central African Republic) ---- Military Forces of the Central African Republic (2016-) ---- Unidentified Armed Group (Central African Republic) ---- Protesters (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Students (Central African Republic) ---- Students (Central African Republic) ---- Teachers (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>Civilians (Central African Republic) ---- Police Forces of the Central African Republic (2016-) ---- Civilians (Central African Republic) ---- Civilians (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Students (Central African Republic) ---- Students (Central African Republic); Taxi Drivers (Central African Republic) ---- Private Security Forces (Central African Republic)</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>On 18 December 2024, a FACA soldier shot and injured a female student near the Avenir School Complex at the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui). The shooting occurred when the FACA forces arrested one civilian and slapped another who retaliated during security checks. The injured student was taken to a community hospital for treatment. ---- On 18 December 2024, students from Avenir School Complex protested near the United Nations Roundabout in Bangui (Arrondissement 1, Bangui, Bangui), condemning the shooting of a fellow student by a FACA soldier (coded separately). The protesters demanded accountability and sanctions against the soldier, criticizing the use of firearms during regular security checks. ---- On 11 February 2025, Gbaloko high school students protested in Bangui (Arrondissement 1, Bangui), to condemn an alleged extortion scheme by the school administration, where exams, assignments, and lessons have allegedly become opportunities for financial exploitation. Police fired live ammunition to suppress protesters. ---- On 25 April 2025, FACA soldiers attacked a student working as a commercial motorbike driver (taxi) in Bangui - 3 (Arrondissement 3, Bangui, Bangui). They punched and kicked him until he collapsed, and left him unconscious on the side of a road. They also looted his mobile phone and motorbike. There were no fatalities. The victim spent two days in a coma. ---- On 30 May 2025, an unidentified armed group attacked the AMA scientific high school in the Kokpa neighborhood in Bangui - 4 (Arrondissement 4, Bangui, Bangui), torturing the security guard (was armed only with a baton), who later died. The attackers looted exam papers, equipment, and vandalized offices. ---- On 14 July 2025, a dozen of contractual teachers protested outside the administrative building in Bangui (Arrondissement 1, Bangui, Bangui), to demand three months of unpaid salaries and denounce unequal payments and lack of support for deployment.</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>2024-12-18 ---- 2024-12-18 ---- 2025-02-11 ---- 2025-04-25 ---- 2025-05-30 ---- 2025-07-14</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Bangui</t>
+        </is>
+      </c>
       <c r="AL74" t="n">
-        <v>0.05791159513132607</v>
+        <v>0.1481596371688042</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CF714</t>
+          <t>CF712</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -7330,7 +7322,7 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CF611</t>
+          <t>CF413</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -7339,31 +7331,31 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>66.09999999999999</v>
+        <v>61</v>
       </c>
       <c r="I75" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
       <c r="J75" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>33.9</v>
+        <v>39</v>
       </c>
       <c r="M75" t="n">
-        <v>50.45</v>
+        <v>16.31</v>
       </c>
       <c r="N75" t="n">
-        <v>9.92</v>
+        <v>3.29</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="P75" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -7372,10 +7364,10 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>8.699999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="T75" t="n">
-        <v>4.35</v>
+        <v>0.47</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -7403,6 +7395,182 @@
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
+        <v>0.02227003293084523</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CF713</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CF412</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CF122;CF123;CF124;CF125;CF126;CF215;CF216;CF244;CF312;CF316;CF321;CF322;CF323;CF331;CF341;CF343;CF344;CF345;CF411;CF412;CF414;CF421;CF422;CF431;CF432;CF433;CF435;CF511;CF521;CF522;CF524;CF531;CF533;CF612;CF613;CF615;CF616;CF621;CF622;CF623;CF631;CF633;CF634;CF711;CF713</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I76" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L76" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="M76" t="n">
+        <v>91.02</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="n">
+        <v>0.05791159513132607</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CF714</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CF611</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CF121;CF211;CF212;CF221;CF222;CF223;CF224;CF241;CF242;CF243;CF313;CF324;CF332;CF333;CF342;CF413;CF423;CF434;CF512;CF611;CF632;CF712;CF714</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I77" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="M77" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="N77" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="n">
         <v>0.003867066654167057</v>
       </c>
     </row>
@@ -7673,13 +7841,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9273CDD-DE4C-45BA-A38B-747F7CE3AA8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C7856C0-BD0D-4BF5-81E1-DA259105CE74}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A783AD56-D92E-4362-858C-4C02A211AAA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DAE5AF-A0C0-46AB-8D49-4096A624603C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E4216EC-8D22-4E22-AC63-85121328CC76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5F620B9-2976-41AE-813B-989DA7EB4FDC}"/>
 </file>